--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126211257</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126211257</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126211257</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126210766</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126211496</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126211548</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126211586</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126211257</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126211257</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126210766</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126211496</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126211548</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126211586</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126211257</v>
+        <v>126210766</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489053</v>
+        <v>489043</v>
       </c>
       <c r="R2" t="n">
-        <v>6824593</v>
+        <v>6824654</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126210766</v>
+        <v>126211496</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489043</v>
+        <v>489008</v>
       </c>
       <c r="R3" t="n">
-        <v>6824654</v>
+        <v>6824533</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126211496</v>
+        <v>126211548</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489008</v>
+        <v>488983</v>
       </c>
       <c r="R4" t="n">
-        <v>6824533</v>
+        <v>6824519</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126211548</v>
+        <v>126211586</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488983</v>
+        <v>488994</v>
       </c>
       <c r="R5" t="n">
-        <v>6824519</v>
+        <v>6824507</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126211586</v>
+        <v>126210853</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488994</v>
+        <v>489067</v>
       </c>
       <c r="R6" t="n">
-        <v>6824507</v>
+        <v>6824660</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1157,6 +1157,200 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126211958</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488919</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6824579</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126211257</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6824593</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31078-2025 artfynd.xlsx
+++ b/artfynd/A 31078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210766</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211548</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211586</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211958</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>